--- a/aq_files/0105.xlsx
+++ b/aq_files/0105.xlsx
@@ -1,101 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Q.No,Question,Type,Difficulty</t>
-  </si>
-  <si>
-    <t>1,What is LSTM (Long Short-Term Memory)? How does it address the limitations of simple RNNs?,Theory,Easy</t>
-  </si>
-  <si>
-    <t>2,Explain the architecture of an LSTM cell. What are the three gates and what role does each gate play?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>3,What is the forget gate in LSTM? Write its mathematical formulation and explain its purpose.,Technical,Medium</t>
-  </si>
-  <si>
-    <t>4,What is the input gate in LSTM? How does it control the flow of new information into the cell state?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>5,What is the output gate in LSTM? How does it determine what information to output from the cell state?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>6,Explain the concept of the cell state in LSTM. How does it help preserve long-term dependencies?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>7,Write the complete mathematical equations for an LSTM cell (forward pass).,Technical,Hard</t>
-  </si>
-  <si>
-    <t>8,What is the difference between LSTM and GRU (Gated Recurrent Unit)? Compare their architectures and complexity.,Theory,Medium</t>
-  </si>
-  <si>
-    <t>9,Write Python code to create an LSTM model using Keras/TensorFlow for text classification.,Coding,Medium</t>
-  </si>
-  <si>
-    <t>10,What is peephole connection in LSTM? How does it improve the standard LSTM architecture?,Technical,Hard</t>
-  </si>
-  <si>
-    <t>11,How do you choose the number of LSTM units in a layer? What factors influence this decision?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>12,What is the impact of dropout on LSTM training? How does recurrent dropout differ from standard dropout?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>13,Write Python code to implement a stacked LSTM with multiple layers for sequence prediction.,Coding,Medium</t>
-  </si>
-  <si>
-    <t>14,How does LSTM handle the vanishing gradient problem? Explain the role of the cell state and forget gate.,Technical,Medium</t>
-  </si>
-  <si>
-    <t>15,What are the computational complexity and memory requirements of LSTM compared to simple RNN?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>16,How do you initialize LSTM weights? What are the recommended initialization strategies?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>17,Write Python code to visualize LSTM cell states and hidden states during training.,Coding,Hard</t>
-  </si>
-  <si>
-    <t>18,What are the limitations of LSTM? Are there scenarios where simple RNN might be preferred?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>19,How do you implement early stopping and model checkpointing for LSTM training?,Practical,Medium</t>
-  </si>
-  <si>
-    <t>20,Explain how LSTM can be used for time series forecasting. Provide code example.,Coding,Hard</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -105,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,118 +316,1033 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Order_ID,Order_Date,Year,Quarter,Month,Month_Num,Week,Region,State,City,Product_Category,Sub_Category,Product_Name,Sales,Profit,Quantity,Discount,Profit_Margin,Customer_Segment,Sales_Rep,Shipping_Cost</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6001,2024-01-01,2024,Q1,January,1,1,North,Illinois,Chicago,Electronics,Computers,MacBook Pro,2499.99,749.98,2,0.10,0.30,Corporate,John Smith,25.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6002,2024-01-01,2024,Q1,January,1,1,North,Illinois,Chicago,Electronics,Accessories,Magic Mouse,89.99,26.99,5,0.05,0.30,Corporate,John Smith,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6003,2024-01-02,2024,Q1,January,1,1,South,Texas,Houston,Clothing,Mens,Designer Jeans,99.99,29.99,8,0.00,0.30,Consumer,Sarah Lee,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6004,2024-01-02,2024,Q1,January,1,1,South,Texas,Austin,Electronics,Monitors,4K Monitor,449.99,134.99,3,0.15,0.30,Consumer,Sarah Lee,18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6005,2024-01-03,2024,Q1,January,1,1,East,New York,New York,Furniture,Chairs,Executive Chair,449.99,134.99,2,0.05,0.30,Corporate,Michael Brown,22.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6006,2024-01-03,2024,Q1,January,1,1,East,New York,Buffalo,Electronics,Keyboards,Mechanical Keyboard,129.99,38.99,4,0.10,0.30,Consumer,Michael Brown,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6007,2024-01-04,2024,Q1,January,1,1,West,California,Los Angeles,Clothing,Womens,Leather Jacket,199.99,59.99,3,0.20,0.30,Home Office,Emily Davis,15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6008,2024-01-04,2024,Q1,January,1,1,West,California,San Francisco,Electronics,Tablets,iPad Air,599.99,179.99,2,0.05,0.30,Corporate,Emily Davis,20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6009,2024-01-05,2024,Q1,January,1,1,North,Illinois,Chicago,Furniture,Lighting,Floor Lamp,89.99,26.99,5,0.00,0.30,Consumer,John Smith,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6010,2024-01-05,2024,Q1,January,1,1,North,Michigan,Detroit,Clothing,Mens,Running Shoes,79.99,23.99,6,0.10,0.30,Consumer,John Smith,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6011,2024-01-08,2024,Q1,January,1,2,South,Texas,Dallas,Electronics,Computers,Gaming Laptop,1599.99,479.99,1,0.15,0.30,Corporate,Sarah Lee,25.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6012,2024-01-08,2024,Q1,January,1,2,East,Pennsylvania,Philadelphia,Electronics,Audio,Headphones,199.99,59.99,3,0.05,0.30,Consumer,Michael Brown,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6013,2024-01-09,2024,Q1,January,1,2,West,California,San Diego,Clothing,Womens,Wool Coat,249.99,74.99,2,0.20,0.30,Home Office,Emily Davis,15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6014,2024-01-09,2024,Q1,January,1,2,North,Ohio,Columbus,Furniture,Storage,Bookshelf,189.99,56.99,2,0.10,0.30,Corporate,John Smith,18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6015,2024-01-10,2024,Q1,January,1,2,South,Florida,Miami,Electronics,Phones,Smartphone,799.99,239.99,3,0.05,0.30,Consumer,Sarah Lee,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6016,2024-01-10,2024,Q1,January,1,2,East,New York,New York,Clothing,Mens,Dress Shirt,69.99,20.99,8,0.00,0.30,Corporate,Michael Brown,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6017,2024-01-11,2024,Q1,January,1,2,West,Oregon,Portland,Electronics,Storage,External SSD,129.99,38.99,3,0.10,0.30,Consumer,Emily Davis,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6018,2024-01-11,2024,Q1,January,1,2,North,Illinois,Chicago,Clothing,Womens,Hoodie,59.99,17.99,10,0.05,0.30,Consumer,John Smith,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6019,2024-01-12,2024,Q1,January,1,2,South,Texas,Austin,Furniture,Desks,Gaming Desk,399.99,119.99,1,0.15,0.30,Corporate,Sarah Lee,25.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6020,2024-01-12,2024,Q1,January,1,2,East,Massachusetts,Boston,Electronics,Accessories,Webcam,89.99,26.99,4,0.10,0.30,Home Office,Michael Brown,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6021,2024-02-01,2024,Q1,February,2,5,West,Washington,Seattle,Electronics,Docks,Docking Station,149.99,44.99,3,0.00,0.30,Consumer,Emily Davis,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6022,2024-02-01,2024,Q1,February,2,5,North,Minnesota,Minneapolis,Clothing,Mens,Winter Parka,199.99,59.99,3,0.05,0.30,Consumer,John Smith,15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6023,2024-02-02,2024,Q1,February,2,5,South,Florida,Orlando,Furniture,Desks,Office Desk,499.99,149.99,2,0.10,0.30,Corporate,Sarah Lee,22.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6024,2024-02-02,2024,Q1,February,2,5,East,New Jersey,Newark,Electronics,Cables,USB-C Hub,49.99,14.99,8,0.00,0.30,Consumer,Michael Brown,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6025,2024-02-03,2024,Q1,February,2,5,West,California,Los Angeles,Clothing,Mens,Casual Blazer,159.99,47.99,4,0.15,0.30,Home Office,Emily Davis,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6026,2024-02-03,2024,Q1,February,2,5,North,Indiana,Indianapolis,Electronics,Accessories,Gaming Mouse,69.99,20.99,8,0.10,0.30,Consumer,John Smith,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6027,2024-02-04,2024,Q1,February,2,5,South,Georgia,Atlanta,Electronics,Printers,Laser Printer,249.99,74.99,2,0.05,0.30,Corporate,Sarah Lee,18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6028,2024-02-04,2024,Q1,February,2,5,East,Virginia,Richmond,Furniture,Chairs,Lounge Chair,329.99,98.99,2,0.20,0.30,Consumer,Michael Brown,22.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6029,2024-02-05,2024,Q1,February,2,6,West,Arizona,Phoenix,Electronics,Batteries,Power Bank,59.99,17.99,12,0.00,0.30,Consumer,Emily Davis,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6030,2024-02-05,2024,Q1,February,2,6,North,Wisconsin,Milwaukee,Clothing,Accessories,Wool Scarf,29.99,8.99,15,0.10,0.30,Consumer,John Smith,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6031,2024-02-06,2024,Q1,February,2,6,South,Texas,Houston,Electronics,Audio,Gaming Headset,139.99,41.99,4,0.05,0.30,Corporate,Sarah Lee,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6032,2024-02-06,2024,Q1,February,2,6,East,New York,Rochester,Furniture,Storage,Night Stand,89.99,26.99,5,0.10,0.30,Home Office,Michael Brown,15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6033,2024-02-07,2024,Q1,February,2,6,West,California,San Jose,Clothing,Mens,Athletic Shoes,119.99,35.99,4,0.15,0.30,Consumer,Emily Davis,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6034,2024-02-07,2024,Q1,February,2,6,North,Missouri,St Louis,Electronics,Wearables,Smart Watch,249.99,74.99,3,0.05,0.30,Consumer,John Smith,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6035,2024-02-08,2024,Q1,February,2,6,South,Florida,Tampa,Electronics,Audio,Bluetooth Speaker,99.99,29.99,6,0.10,0.30,Corporate,Sarah Lee,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6036,2024-02-08,2024,Q1,February,2,6,East,Pennsylvania,Pittsburgh,Clothing,Womens,Cashmere Sweater,129.99,38.99,5,0.00,0.30,Consumer,Michael Brown,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6037,2024-02-09,2024,Q1,February,2,6,West,Oregon,Eugene,Furniture,Storage,Bookshelf,159.99,47.99,3,0.05,0.30,Home Office,Emily Davis,18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6038,2024-02-09,2024,Q1,February,2,6,North,Iowa,Des Moines,Electronics,Networking,Mesh Router,119.99,35.99,4,0.10,0.30,Consumer,John Smith,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6039,2024-02-10,2024,Q1,February,2,6,South,Texas,San Antonio,Clothing,Mens,Golf Polo,49.99,14.99,12,0.15,0.30,Consumer,Sarah Lee,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6040,2024-02-10,2024,Q1,February,2,6,West,Washington,Spokane,Electronics,Components,Graphics Card,549.99,164.99,2,0.20,0.30,Corporate,Emily Davis,18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6041,2024-03-01,2024,Q1,March,3,9,North,Illinois,Chicago,Electronics,Computers,Desktop PC,1299.99,389.99,2,0.05,0.30,Corporate,John Smith,25.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6042,2024-03-01,2024,Q1,March,3,9,South,Texas,Austin,Clothing,Womens,Yoga Pants,54.99,16.49,8,0.00,0.30,Consumer,Sarah Lee,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6043,2024-03-02,2024,Q1,March,3,9,East,New York,New York,Furniture,Tables,Coffee Table,279.99,83.99,2,0.10,0.30,Corporate,Michael Brown,22.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6044,2024-03-02,2024,Q1,March,3,9,West,California,Los Angeles,Electronics,Smart Home,Smart Speaker,99.99,29.99,5,0.00,0.30,Home Office,Emily Davis,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6045,2024-03-03,2024,Q1,March,3,9,North,Michigan,Detroit,Clothing,Accessories,Baseball Cap,24.99,7.49,12,0.05,0.30,Consumer,John Smith,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6046,2024-03-03,2024,Q1,March,3,9,South,Florida,Miami,Electronics,Drones,Quadcopter,399.99,119.99,2,0.10,0.30,Corporate,Sarah Lee,18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6047,2024-03-04,2024,Q1,March,3,9,East,Pennsylvania,Philadelphia,Furniture,Decor,Wall Mirror,79.99,23.99,4,0.00,0.30,Consumer,Michael Brown,12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6048,2024-03-04,2024,Q1,March,3,9,West,Oregon,Portland,Clothing,Mens,Flannel Shirt,54.99,16.49,6,0.10,0.30,Home Office,Emily Davis,10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6049,2024-03-05,2024,Q1,March,3,10,North,Ohio,Columbus,Electronics,Streaming,Streaming Stick,39.99,11.99,8,0.05,0.30,Consumer,John Smith,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>ORD-6050,2024-03-05,2024,Q1,March,3,10,South,Georgia,Atlanta,Clothing,Womens,Leggings,34.99,10.49,10,0.00,0.30,Consumer,Sarah Lee,8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3051,2024-02-11,West,California,Los Angeles,Electronics,Monitors,Ultrawide Monitor,549.99,2,549.98,0.15,22.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3052,2024-02-11,North,Illinois,Chicago,Clothing,Mens,Denim Jacket,89.99,5,224.98,0.10,12.00,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3053,2024-02-12,South,Texas,Houston,Furniture,Chairs,Gaming Chair,299.99,2,299.98,0.05,22.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3054,2024-02-12,East,New York,Buffalo,Electronics,Audio,Portable Speaker,79.99,4,159.98,0.00,10.00,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3055,2024-02-13,West,Washington,Seattle,Clothing,Womens,Rain Jacket,129.99,3,194.98,0.15,12.00,Home Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3056,2024-02-13,North,Minnesota,Minneapolis,Electronics,Storage,Portable SSD,89.99,5,224.98,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3057,2024-02-14,South,Florida,Orlando,Electronics,Phones,Smartphone Case,29.99,15,224.85,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3058,2024-02-14,East,Massachusetts,Boston,Furniture,Lighting,Desk Lamp,59.99,6,179.97,0.05,12.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3059,2024-02-15,West,California,San Diego,Clothing,Accessories,Leather Belt,39.99,8,159.96,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3060,2024-02-15,North,Ohio,Columbus,Electronics,Accessories,Phone Stand,19.99,12,119.94,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing the Running Total (Cumulative Sum) of Sales by Order Date. What was the cumulative sales by February 1st, 2024?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing the Running Total of Sales by Region (ordered alphabetically). Which region has the highest cumulative sales when regions are ordered A-Z?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Percent of Total Sales by Product Category. What percentage of total sales does Electronics contribute?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Percent of Total Sales by Customer Segment. Which customer segment contributes the most to total sales?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Percent of Total Sales by Region within each Product Category (Table Down). What percentage of Electronics sales comes from the West region?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Rank of Products by Sales (highest to lowest). Which product is ranked #1? Which product is ranked #10?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Rank of Regions by Profit. Which region is ranked #1 in profit? Which region is ranked last?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Moving Average (3-period) of Sales by Month. What is the moving average for March?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Moving Average (4-period) of Sales by Week. What is the moving average for Week 6?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Year-over-Year Growth. Compare March 2024 vs March 2023. What is the growth percentage?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Month-over-Month Growth. What is the growth percentage from January to February?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Difference from Average Sales by Region. Which region is above average? Which region is below average?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Difference from Previous Month. What was the absolute sales difference between February and January?</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Percent Difference from Previous Month. What was the percentage change from January to February?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Index (starting at 1) for Products ordered by Sales. What is the index value for the 5th highest product?</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing First Value of Sales by Region. What is the first region in alphabetical order and what is its sales value?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Last Value of Sales by Region. What is the last region in alphabetical order and what is its sales value?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Running Average (Cumulative Average) of Sales by Month. What is the running average by March?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Window Sum for the last 2 months. What is the total sales for February and March combined?</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="0" t="n">
         <v>20</v>
       </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Create Table Calculations</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Table Calculation showing Window Maximum for quarterly sales. What was the maximum sales month in Q1?</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>